--- a/tests/Issue_Files/xlsx/XlsxIssue82_WideTable.xlsx
+++ b/tests/Issue_Files/xlsx/XlsxIssue82_WideTable.xlsx
@@ -7999,7 +7999,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L121"/>
   <pageMargins left="0.35" right="0.35" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1"/>
   <tableParts count="1">
